--- a/affiliate_data/อาหารและเครื่องดื่ม.xlsx
+++ b/affiliate_data/อาหารและเครื่องดื่ม.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Shopee Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shopee Products" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5660,6 +5660,136 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Lifinity ชั้นวางจาน ที่คว่ำจาน 120/105ซม ชั้นวางของในครัว</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m6m8v000vb5b5e.webp</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>678.00</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ขายได้ 6พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/8442385823</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qc9ZkOEib</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>JTL เครื่องปั่นน้ำผลไม้ สมูทตี้ มอเตอร์รอบสูงพิเศษ BD-388</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcacyy53vboz1c.webp</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1590.00</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ขายได้ 20พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/11123672265</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KpdJo13zt</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>(สินค้าขายดี) 1 ขวด ขวด1000g น้ำผึ้งโพรงป่าแท้เดือน5 Natural Honey ไม่ใช่ผึ้งฟาร์ม ไม่ผ่านความร้อน ไม่ผสม เก็บช่วงแล้ง</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-824g3-mptu5ddu3w9acc.webp</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>399.00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ขายได้ 2พัน+ ชิ้น</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://shopee.co.th/product/0/11105780259</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VNz8UNscQ</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
